--- a/mainWidget/mainWidget/src/database/标准数据库.xlsx
+++ b/mainWidget/mainWidget/src/database/标准数据库.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSProject\git\GFApp\mainWidget\mainWidget\src\database\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{212C3A26-63E1-4249-8DE6-21E77CD64776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -79,18 +73,18 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>爆炸冲击波试验[kg]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>殉爆试验[mm]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆炸冲击波试验[g]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -422,14 +416,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
@@ -468,10 +462,10 @@
         <v>12</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
@@ -503,7 +497,7 @@
         <v>1830</v>
       </c>
       <c r="J2" s="1">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="K2" s="1">
         <v>100</v>
@@ -538,7 +532,7 @@
         <v>1830</v>
       </c>
       <c r="J3" s="1">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="K3" s="1">
         <v>100</v>

--- a/mainWidget/mainWidget/src/database/标准数据库.xlsx
+++ b/mainWidget/mainWidget/src/database/标准数据库.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -33,22 +33,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>HJB929</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>海军弹药安全性试验与评估</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>GJB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>国家军用弹药安全性试验与评估</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>跌落试验[m]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -78,6 +66,14 @@
   </si>
   <si>
     <t>爆炸冲击波试验[g]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HJB929-2022</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>军用混合炸药配方性能试验方法</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -416,7 +412,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -427,6 +423,7 @@
   <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="2" max="2" width="13.640625" customWidth="1"/>
     <col min="3" max="3" width="33.42578125" customWidth="1"/>
     <col min="4" max="4" width="12.5" customWidth="1"/>
     <col min="5" max="5" width="12.85546875" customWidth="1"/>
@@ -444,28 +441,28 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
@@ -473,10 +470,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="D2" s="1">
         <v>37.5</v>
@@ -507,11 +504,11 @@
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
+      <c r="B3" s="1">
+        <v>30131106</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1">
         <v>37.5</v>
